--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J130-CNAMAmeliSecteurConventionnement-RASS.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J130-CNAMAmeliSecteurConventionnement-RASS.xlsx
@@ -108,19 +108,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>Secteur 1 ou conventionné</t>
+    <t>Conventionné</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Conventionné Dépassement Permanent</t>
+    <t>Conventionné avec dépassement</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Secteur 2</t>
+    <t>Conventionné avec honoraires libres</t>
   </si>
   <si>
     <t/>
